--- a/outputs/all_metrics.xlsx
+++ b/outputs/all_metrics.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vachr\OneDrive\Документы\coffee-books-project\outputs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B53EB2EB-6024-43D1-8C46-35388B5B0156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="best_day" sheetId="1" r:id="rId1"/>
@@ -13,16 +19,69 @@
     <sheet name="weekday_vs_weekend" sheetId="4" r:id="rId4"/>
     <sheet name="worst_day" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="16">
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>day_type</t>
+  </si>
+  <si>
+    <t>revenue</t>
+  </si>
+  <si>
+    <t>transactions</t>
+  </si>
+  <si>
+    <t>weekend</t>
+  </si>
+  <si>
+    <t>weekday</t>
+  </si>
+  <si>
+    <t>weekday_name</t>
+  </si>
+  <si>
+    <t>weekday_num</t>
+  </si>
+  <si>
+    <t>avg_check</t>
+  </si>
+  <si>
+    <t>вс</t>
+  </si>
+  <si>
+    <t>пн</t>
+  </si>
+  <si>
+    <t>вт</t>
+  </si>
+  <si>
+    <t>ср</t>
+  </si>
+  <si>
+    <t>чт</t>
+  </si>
+  <si>
+    <t>пт</t>
+  </si>
+  <si>
+    <t>сб</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,17 +126,25 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -115,7 +182,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -149,6 +216,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -183,9 +251,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -358,43 +427,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>day_type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>transactions</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>45347</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B2" t="s">
+        <v>4</v>
       </c>
       <c r="C2">
         <v>43290</v>
@@ -409,43 +468,34 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D91"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>day_type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>transactions</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>45292</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B2" t="s">
+        <v>5</v>
       </c>
       <c r="C2">
         <v>23780</v>
@@ -454,14 +504,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>45293</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B3" t="s">
+        <v>5</v>
       </c>
       <c r="C3">
         <v>29300</v>
@@ -470,14 +518,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>45294</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B4" t="s">
+        <v>5</v>
       </c>
       <c r="C4">
         <v>25890</v>
@@ -486,14 +532,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>45295</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B5" t="s">
+        <v>5</v>
       </c>
       <c r="C5">
         <v>17330</v>
@@ -502,14 +546,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>45296</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B6" t="s">
+        <v>5</v>
       </c>
       <c r="C6">
         <v>21350</v>
@@ -518,14 +560,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>45297</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B7" t="s">
+        <v>4</v>
       </c>
       <c r="C7">
         <v>24940</v>
@@ -534,14 +574,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>45298</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B8" t="s">
+        <v>4</v>
       </c>
       <c r="C8">
         <v>27070</v>
@@ -550,14 +588,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>45299</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B9" t="s">
+        <v>5</v>
       </c>
       <c r="C9">
         <v>20320</v>
@@ -566,14 +602,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>45300</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B10" t="s">
+        <v>5</v>
       </c>
       <c r="C10">
         <v>14250</v>
@@ -582,14 +616,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>45301</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B11" t="s">
+        <v>5</v>
       </c>
       <c r="C11">
         <v>23870</v>
@@ -598,14 +630,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>45302</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B12" t="s">
+        <v>5</v>
       </c>
       <c r="C12">
         <v>26720</v>
@@ -614,14 +644,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>45303</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B13" t="s">
+        <v>5</v>
       </c>
       <c r="C13">
         <v>27300</v>
@@ -630,14 +658,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>45304</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B14" t="s">
+        <v>4</v>
       </c>
       <c r="C14">
         <v>17090</v>
@@ -646,14 +672,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>45305</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B15" t="s">
+        <v>4</v>
       </c>
       <c r="C15">
         <v>25960</v>
@@ -662,14 +686,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>45306</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B16" t="s">
+        <v>5</v>
       </c>
       <c r="C16">
         <v>18560</v>
@@ -678,14 +700,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>45307</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B17" t="s">
+        <v>5</v>
       </c>
       <c r="C17">
         <v>22650</v>
@@ -694,14 +714,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>45308</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B18" t="s">
+        <v>5</v>
       </c>
       <c r="C18">
         <v>25700</v>
@@ -710,14 +728,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>45309</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B19" t="s">
+        <v>5</v>
       </c>
       <c r="C19">
         <v>22040</v>
@@ -726,14 +742,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>45310</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B20" t="s">
+        <v>5</v>
       </c>
       <c r="C20">
         <v>33930</v>
@@ -742,14 +756,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>45311</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B21" t="s">
+        <v>4</v>
       </c>
       <c r="C21">
         <v>22380</v>
@@ -758,14 +770,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>45312</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B22" t="s">
+        <v>4</v>
       </c>
       <c r="C22">
         <v>26600</v>
@@ -774,14 +784,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>45313</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B23" t="s">
+        <v>5</v>
       </c>
       <c r="C23">
         <v>16080</v>
@@ -790,14 +798,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>45314</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B24" t="s">
+        <v>5</v>
       </c>
       <c r="C24">
         <v>34720</v>
@@ -806,14 +812,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>45315</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B25" t="s">
+        <v>5</v>
       </c>
       <c r="C25">
         <v>33000</v>
@@ -822,14 +826,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>45316</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B26" t="s">
+        <v>5</v>
       </c>
       <c r="C26">
         <v>30030</v>
@@ -838,14 +840,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>45317</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B27" t="s">
+        <v>5</v>
       </c>
       <c r="C27">
         <v>21310</v>
@@ -854,14 +854,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>45318</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B28" t="s">
+        <v>4</v>
       </c>
       <c r="C28">
         <v>35000</v>
@@ -870,14 +868,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>45319</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B29" t="s">
+        <v>4</v>
       </c>
       <c r="C29">
         <v>22160</v>
@@ -886,14 +882,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>45320</v>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B30" t="s">
+        <v>5</v>
       </c>
       <c r="C30">
         <v>14640</v>
@@ -902,14 +896,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>45321</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B31" t="s">
+        <v>5</v>
       </c>
       <c r="C31">
         <v>22510</v>
@@ -918,14 +910,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>45322</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B32" t="s">
+        <v>5</v>
       </c>
       <c r="C32">
         <v>29810</v>
@@ -934,14 +924,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>45323</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B33" t="s">
+        <v>5</v>
       </c>
       <c r="C33">
         <v>27270</v>
@@ -950,14 +938,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>45324</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B34" t="s">
+        <v>5</v>
       </c>
       <c r="C34">
         <v>17690</v>
@@ -966,14 +952,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>45325</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B35" t="s">
+        <v>4</v>
       </c>
       <c r="C35">
         <v>32250</v>
@@ -982,14 +966,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>45326</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B36" t="s">
+        <v>4</v>
       </c>
       <c r="C36">
         <v>21890</v>
@@ -998,14 +980,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>45327</v>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B37" t="s">
+        <v>5</v>
       </c>
       <c r="C37">
         <v>23510</v>
@@ -1014,14 +994,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>45328</v>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B38" t="s">
+        <v>5</v>
       </c>
       <c r="C38">
         <v>33030</v>
@@ -1030,14 +1008,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>45329</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B39" t="s">
+        <v>5</v>
       </c>
       <c r="C39">
         <v>28330</v>
@@ -1046,14 +1022,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>45330</v>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B40" t="s">
+        <v>5</v>
       </c>
       <c r="C40">
         <v>18750</v>
@@ -1062,14 +1036,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>45331</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B41" t="s">
+        <v>5</v>
       </c>
       <c r="C41">
         <v>26210</v>
@@ -1078,14 +1050,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>45332</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B42" t="s">
+        <v>4</v>
       </c>
       <c r="C42">
         <v>24870</v>
@@ -1094,14 +1064,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>45333</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B43" t="s">
+        <v>4</v>
       </c>
       <c r="C43">
         <v>25530</v>
@@ -1110,14 +1078,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>45334</v>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B44" t="s">
+        <v>5</v>
       </c>
       <c r="C44">
         <v>30060</v>
@@ -1126,14 +1092,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>45335</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B45" t="s">
+        <v>5</v>
       </c>
       <c r="C45">
         <v>21700</v>
@@ -1142,14 +1106,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>45336</v>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B46" t="s">
+        <v>5</v>
       </c>
       <c r="C46">
         <v>23400</v>
@@ -1158,14 +1120,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>45337</v>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B47" t="s">
+        <v>5</v>
       </c>
       <c r="C47">
         <v>34740</v>
@@ -1174,14 +1134,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>45338</v>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B48" t="s">
+        <v>5</v>
       </c>
       <c r="C48">
         <v>17700</v>
@@ -1190,14 +1148,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>45339</v>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B49" t="s">
+        <v>4</v>
       </c>
       <c r="C49">
         <v>28790</v>
@@ -1206,14 +1162,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>45340</v>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B50" t="s">
+        <v>4</v>
       </c>
       <c r="C50">
         <v>16030</v>
@@ -1222,14 +1176,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>45341</v>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B51" t="s">
+        <v>5</v>
       </c>
       <c r="C51">
         <v>18270</v>
@@ -1238,14 +1190,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>45342</v>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B52" t="s">
+        <v>5</v>
       </c>
       <c r="C52">
         <v>33820</v>
@@ -1254,14 +1204,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>45343</v>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B53" t="s">
+        <v>5</v>
       </c>
       <c r="C53">
         <v>19330</v>
@@ -1270,14 +1218,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>45344</v>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B54" t="s">
+        <v>5</v>
       </c>
       <c r="C54">
         <v>31890</v>
@@ -1286,14 +1232,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>45345</v>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B55" t="s">
+        <v>5</v>
       </c>
       <c r="C55">
         <v>31050</v>
@@ -1302,14 +1246,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>45346</v>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B56" t="s">
+        <v>4</v>
       </c>
       <c r="C56">
         <v>14540</v>
@@ -1318,14 +1260,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>45347</v>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B57" t="s">
+        <v>4</v>
       </c>
       <c r="C57">
         <v>43290</v>
@@ -1334,14 +1274,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>45348</v>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B58" t="s">
+        <v>5</v>
       </c>
       <c r="C58">
         <v>19590</v>
@@ -1350,14 +1288,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>45349</v>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B59" t="s">
+        <v>5</v>
       </c>
       <c r="C59">
         <v>37680</v>
@@ -1366,14 +1302,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>45350</v>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B60" t="s">
+        <v>5</v>
       </c>
       <c r="C60">
         <v>14840</v>
@@ -1382,14 +1316,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>45351</v>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B61" t="s">
+        <v>5</v>
       </c>
       <c r="C61">
         <v>32830</v>
@@ -1398,14 +1330,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>45352</v>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B62" t="s">
+        <v>5</v>
       </c>
       <c r="C62">
         <v>27180</v>
@@ -1414,14 +1344,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>45353</v>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B63" t="s">
+        <v>4</v>
       </c>
       <c r="C63">
         <v>37020</v>
@@ -1430,14 +1358,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>45354</v>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B64" t="s">
+        <v>4</v>
       </c>
       <c r="C64">
         <v>22270</v>
@@ -1446,14 +1372,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>45355</v>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B65" t="s">
+        <v>5</v>
       </c>
       <c r="C65">
         <v>31790</v>
@@ -1462,14 +1386,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>45356</v>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B66" t="s">
+        <v>5</v>
       </c>
       <c r="C66">
         <v>25390</v>
@@ -1478,14 +1400,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>45357</v>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B67" t="s">
+        <v>5</v>
       </c>
       <c r="C67">
         <v>23120</v>
@@ -1494,14 +1414,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>45358</v>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B68" t="s">
+        <v>5</v>
       </c>
       <c r="C68">
         <v>24320</v>
@@ -1510,14 +1428,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>45359</v>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B69" t="s">
+        <v>5</v>
       </c>
       <c r="C69">
         <v>32020</v>
@@ -1526,14 +1442,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>45360</v>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B70" t="s">
+        <v>4</v>
       </c>
       <c r="C70">
         <v>37000</v>
@@ -1542,14 +1456,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>45361</v>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B71" t="s">
+        <v>4</v>
       </c>
       <c r="C71">
         <v>21190</v>
@@ -1558,14 +1470,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>45362</v>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B72" t="s">
+        <v>5</v>
       </c>
       <c r="C72">
         <v>22810</v>
@@ -1574,14 +1484,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>45363</v>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B73" t="s">
+        <v>5</v>
       </c>
       <c r="C73">
         <v>34020</v>
@@ -1590,14 +1498,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>45364</v>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B74" t="s">
+        <v>5</v>
       </c>
       <c r="C74">
         <v>35550</v>
@@ -1606,14 +1512,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>45365</v>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B75" t="s">
+        <v>5</v>
       </c>
       <c r="C75">
         <v>24620</v>
@@ -1622,14 +1526,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>45366</v>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B76" t="s">
+        <v>5</v>
       </c>
       <c r="C76">
         <v>28000</v>
@@ -1638,14 +1540,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>45367</v>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B77" t="s">
+        <v>4</v>
       </c>
       <c r="C77">
         <v>22480</v>
@@ -1654,14 +1554,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>45368</v>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B78" t="s">
+        <v>4</v>
       </c>
       <c r="C78">
         <v>23590</v>
@@ -1670,14 +1568,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>45369</v>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B79" t="s">
+        <v>5</v>
       </c>
       <c r="C79">
         <v>28230</v>
@@ -1686,14 +1582,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>45370</v>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B80" t="s">
+        <v>5</v>
       </c>
       <c r="C80">
         <v>18240</v>
@@ -1702,14 +1596,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>45371</v>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B81" t="s">
+        <v>5</v>
       </c>
       <c r="C81">
         <v>35050</v>
@@ -1718,14 +1610,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>45372</v>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B82" t="s">
+        <v>5</v>
       </c>
       <c r="C82">
         <v>20900</v>
@@ -1734,14 +1624,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>45373</v>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B83" t="s">
+        <v>5</v>
       </c>
       <c r="C83">
         <v>30130</v>
@@ -1750,14 +1638,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>45374</v>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B84" t="s">
+        <v>4</v>
       </c>
       <c r="C84">
         <v>29120</v>
@@ -1766,14 +1652,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>45375</v>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B85" t="s">
+        <v>4</v>
       </c>
       <c r="C85">
         <v>29080</v>
@@ -1782,14 +1666,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>45376</v>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B86" t="s">
+        <v>5</v>
       </c>
       <c r="C86">
         <v>30880</v>
@@ -1798,14 +1680,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>45377</v>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B87" t="s">
+        <v>5</v>
       </c>
       <c r="C87">
         <v>19540</v>
@@ -1814,14 +1694,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>45378</v>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B88" t="s">
+        <v>5</v>
       </c>
       <c r="C88">
         <v>32480</v>
@@ -1830,14 +1708,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>45379</v>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B89" t="s">
+        <v>5</v>
       </c>
       <c r="C89">
         <v>23370</v>
@@ -1846,14 +1722,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>45380</v>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B90" t="s">
+        <v>5</v>
       </c>
       <c r="C90">
         <v>24010</v>
@@ -1862,14 +1736,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>45381</v>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="B91" t="s">
+        <v>4</v>
       </c>
       <c r="C91">
         <v>24260</v>
@@ -1884,55 +1756,39 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>weekday_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>weekday_num</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>day_type</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>transactions</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>avg_check</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>вс</t>
-        </is>
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="C2" t="s">
+        <v>4</v>
       </c>
       <c r="D2">
         <v>304660</v>
@@ -1944,19 +1800,15 @@
         <v>1190.078125</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>пн</t>
-        </is>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="C3" t="s">
+        <v>5</v>
       </c>
       <c r="D3">
         <v>298520</v>
@@ -1968,19 +1820,15 @@
         <v>1175.275590551181</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>вт</t>
-        </is>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="C4" t="s">
+        <v>5</v>
       </c>
       <c r="D4">
         <v>346850</v>
@@ -1992,19 +1840,15 @@
         <v>1144.719471947195</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ср</t>
-        </is>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="C5" t="s">
+        <v>5</v>
       </c>
       <c r="D5">
         <v>350370</v>
@@ -2013,22 +1857,18 @@
         <v>307</v>
       </c>
       <c r="F5">
-        <v>1141.270358306189</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>чт</t>
-        </is>
+        <v>1141.2703583061891</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>13</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="C6" t="s">
+        <v>5</v>
       </c>
       <c r="D6">
         <v>334810</v>
@@ -2037,22 +1877,18 @@
         <v>303</v>
       </c>
       <c r="F6">
-        <v>1104.983498349835</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>пт</t>
-        </is>
+        <v>1104.9834983498349</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>14</v>
       </c>
       <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="C7" t="s">
+        <v>5</v>
       </c>
       <c r="D7">
         <v>337880</v>
@@ -2064,19 +1900,15 @@
         <v>1206.714285714286</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>сб</t>
-        </is>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>15</v>
       </c>
       <c r="B8">
         <v>7</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+      <c r="C8" t="s">
+        <v>4</v>
       </c>
       <c r="D8">
         <v>349740</v>
@@ -2094,37 +1926,27 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>day_type</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>transactions</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>avg_check</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
       </c>
       <c r="B2">
         <v>1668430</v>
@@ -2133,14 +1955,12 @@
         <v>1447</v>
       </c>
       <c r="D2">
-        <v>1153.026952315135</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
+        <v>1153.0269523151351</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
       </c>
       <c r="B3">
         <v>654400</v>
@@ -2149,7 +1969,7 @@
         <v>553</v>
       </c>
       <c r="D3">
-        <v>1183.363471971067</v>
+        <v>1183.3634719710669</v>
       </c>
     </row>
   </sheetData>
@@ -2158,43 +1978,33 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>day_type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>transactions</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>45300</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
+      <c r="B2" t="s">
+        <v>5</v>
       </c>
       <c r="C2">
         <v>14250</v>
